--- a/tests/M4-calendar.xlsx
+++ b/tests/M4-calendar.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -454,6 +454,7 @@
     <col width="24.140625" customWidth="1" min="7" max="7"/>
     <col width="26.5703125" customWidth="1" min="8" max="8"/>
     <col width="30.42578125" customWidth="1" min="9" max="9"/>
+    <col width="62" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,6 +513,11 @@
           <t>Test Type</t>
         </is>
       </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Result</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="57.95" customHeight="1">
       <c r="A2" s="3" t="n">
@@ -557,6 +563,11 @@
       </c>
       <c r="J2" s="4" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr"/>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS on the phone. 19 Mar 2026 shows Thu 19 Mar, kṛṣṇa amāvāsyā, Hyderabad, and no observance card. The Hyderabad CSV has tithi 15, kṛṣṇa, Phālguna, and no observance.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="57.95" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -602,6 +613,11 @@
       </c>
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. 14 Sep 2026 shows Vinayaka Chavithi. The CSV has śukla 3, Bhādrapada, obs.vinayaka-chavithi.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="57.95" customHeight="1">
       <c r="A4" s="3" t="n">
@@ -646,6 +662,11 @@
       </c>
       <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. 11 Oct 2026 shows Sun 11 Oct, śukla pratipat, Hyderabad, and no observance card. The CSV has śukla 1, Āśvayuja, and no observance.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="57.95" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -689,6 +710,11 @@
       </c>
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hyderabad and Vijayawada 2026 CSVs are in tests/calendar-export. The three dates match the phone. Comparison with the TTD panchangam is still open, so no override was added.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="57.95" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -777,6 +803,11 @@
       </c>
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. Day 14 opens the Vinayaka Chavithi page. What families do is open, and the katha card is under it.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="57.95" customHeight="1">
       <c r="A8" s="3" t="n">
@@ -1176,6 +1207,11 @@
       </c>
       <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS. With airplane mode on and no network, the calendar month still opens.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
